--- a/data/trans_camb/P6906-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 32,6</t>
+          <t>-15,35; 32,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 20,55</t>
+          <t>-20,52; 20,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 12,99</t>
+          <t>-34,08; 17,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 40,02</t>
+          <t>-12,96; 39,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 40,33</t>
+          <t>-4,43; 41,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 33,53</t>
+          <t>-14,51; 36,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 28,14</t>
+          <t>-5,82; 29,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 22,35</t>
+          <t>-9,42; 22,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 15,79</t>
+          <t>-21,53; 17,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 135,31</t>
+          <t>-32,77; 141,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 87,02</t>
+          <t>-44,44; 90,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 54,89</t>
+          <t>-79,01; 75,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 274,26</t>
+          <t>-33,77; 319,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 296,92</t>
+          <t>-12,51; 297,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 237,78</t>
+          <t>-40,99; 286,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 116,7</t>
+          <t>-14,59; 121,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 95,5</t>
+          <t>-21,99; 93,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,27; 66,28</t>
+          <t>-55,17; 78,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 23,39</t>
+          <t>-9,61; 25,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 5,33</t>
+          <t>-21,11; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 26,86</t>
+          <t>-13,86; 26,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 23,09</t>
+          <t>-16,51; 23,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 26,79</t>
+          <t>-11,08; 25,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 35,42</t>
+          <t>-3,41; 33,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 18,28</t>
+          <t>-7,77; 18,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 9,61</t>
+          <t>-13,41; 9,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 24,09</t>
+          <t>-3,49; 23,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 166,36</t>
+          <t>-32,68; 168,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 39,07</t>
+          <t>-69,98; 61,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 179,45</t>
+          <t>-51,25; 184,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 260,38</t>
+          <t>-68,99; 288,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 353,8</t>
+          <t>-43,43; 350,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 493,95</t>
+          <t>-13,05; 439,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 117,74</t>
+          <t>-29,27; 114,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 66,06</t>
+          <t>-49,7; 66,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 168,71</t>
+          <t>-15,46; 150,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 30,58</t>
+          <t>-11,15; 31,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 1,49</t>
+          <t>-31,44; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 13,35</t>
+          <t>-20,54; 11,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 40,96</t>
+          <t>-9,29; 40,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 35,5</t>
+          <t>-18,86; 34,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 25,38</t>
+          <t>-12,46; 25,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 26,15</t>
+          <t>-5,15; 26,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 8,3</t>
+          <t>-21,71; 8,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 14,76</t>
+          <t>-10,76; 14,41</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 393,74</t>
+          <t>-51,53; 458,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,14; 273,05</t>
+          <t>-74,31; 176,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,89; —</t>
+          <t>-67,68; 891,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 545,07</t>
+          <t>-44,44; 615,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,58; 309,11</t>
+          <t>-30,8; 286,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 309,06</t>
+          <t>-100,0; 167,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 175,53</t>
+          <t>-45,24; 152,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 28,87</t>
+          <t>-5,57; 28,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 47,85</t>
+          <t>3,62; 47,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 33,67</t>
+          <t>-9,74; 33,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 47,8</t>
+          <t>2,87; 46,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 54,67</t>
+          <t>12,39; 52,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 32,16</t>
+          <t>-20,36; 31,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 29,88</t>
+          <t>2,24; 29,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 42,93</t>
+          <t>12,63; 43,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 22,52</t>
+          <t>-11,69; 21,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 235,95</t>
+          <t>-23,84; 246,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 413,43</t>
+          <t>12,38; 375,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,06; 293,72</t>
+          <t>-41,59; 272,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,48; —</t>
+          <t>-28,21; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,12; —</t>
+          <t>13,17; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,13; —</t>
+          <t>-64,07; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 259,6</t>
+          <t>2,65; 251,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,31; 398,7</t>
+          <t>49,56; 417,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 178,49</t>
+          <t>-45,62; 166,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 13,2</t>
+          <t>-23,53; 12,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 54,94</t>
+          <t>-4,02; 53,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 15,91</t>
+          <t>-17,88; 14,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 44,98</t>
+          <t>-32,46; 44,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 69,83</t>
+          <t>-28,88; 68,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 13,81</t>
+          <t>-46,6; 12,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 18,39</t>
+          <t>-17,85; 19,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 49,76</t>
+          <t>-2,37; 48,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 10,99</t>
+          <t>-17,43; 10,66</t>
         </is>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 496,77</t>
+          <t>-84,56; 417,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 1278,5</t>
+          <t>-37,04; 1160,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,33; 388,58</t>
+          <t>-80,75; 364,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 10,94</t>
+          <t>-23,96; 11,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 5,45</t>
+          <t>-30,91; 4,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 12,49</t>
+          <t>-24,38; 11,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 48,39</t>
+          <t>-15,24; 47,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 80,36</t>
+          <t>0,43; 80,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 28,9</t>
+          <t>-17,35; 31,6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 15,28</t>
+          <t>-13,02; 16,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 19,79</t>
+          <t>-15,7; 22,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 14,48</t>
+          <t>-14,29; 14,95</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 111,39</t>
+          <t>-76,04; 108,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 89,85</t>
+          <t>-100,0; 90,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 123,91</t>
+          <t>-78,49; 123,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,25; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,6; —</t>
+          <t>-29,88; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,16; —</t>
+          <t>-55,93; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 133,56</t>
+          <t>-51,2; 137,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,73; 156,21</t>
+          <t>-69,82; 182,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 124,62</t>
+          <t>-49,52; 126,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 21,28</t>
+          <t>-8,0; 22,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 14,43</t>
+          <t>-10,99; 15,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 13,82</t>
+          <t>-10,85; 14,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 21,98</t>
+          <t>-16,02; 19,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 16,03</t>
+          <t>-20,99; 18,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 23,15</t>
+          <t>-11,67; 23,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 17,0</t>
+          <t>-5,45; 16,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 10,74</t>
+          <t>-8,53; 12,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 13,73</t>
+          <t>-4,05; 15,08</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 180,8</t>
+          <t>-38,92; 178,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 127,7</t>
+          <t>-49,54; 137,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-50,11; 118,13</t>
+          <t>-47,67; 128,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 119,69</t>
+          <t>-45,72; 118,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 97,44</t>
+          <t>-56,81; 111,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 168,08</t>
+          <t>-31,72; 142,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 112,01</t>
+          <t>-23,47; 105,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 68,11</t>
+          <t>-34,11; 83,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 87,01</t>
+          <t>-18,05; 94,9</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 2,43</t>
+          <t>-24,91; 4,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 20,87</t>
+          <t>-13,33; 21,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-28,96; -6,05</t>
+          <t>-29,37; -6,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 23,71</t>
+          <t>-21,38; 25,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 20,02</t>
+          <t>-26,88; 18,33</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 1,36</t>
+          <t>-30,32; -0,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 4,86</t>
+          <t>-19,24; 5,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 13,99</t>
+          <t>-14,25; 13,83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -6,3</t>
+          <t>-25,21; -7,25</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 15,67</t>
+          <t>-82,55; 22,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 98,89</t>
+          <t>-46,14; 96,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-86,92; -8,94</t>
+          <t>-89,1; -20,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 118,36</t>
+          <t>-65,78; 127,29</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 100,39</t>
+          <t>-81,61; 87,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-79,34; 8,78</t>
+          <t>-78,25; 0,69</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 23,39</t>
+          <t>-63,01; 23,06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 60,55</t>
+          <t>-47,03; 65,52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,72; -25,93</t>
+          <t>-77,89; -27,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 9,55</t>
+          <t>-3,41; 9,42</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,37</t>
+          <t>-5,53; 6,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 3,0</t>
+          <t>-9,5; 3,13</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 16,64</t>
+          <t>-1,48; 16,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,68; 19,31</t>
+          <t>2,42; 18,71</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,13</t>
+          <t>-5,74; 10,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,55</t>
+          <t>0,21; 10,42</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,4</t>
+          <t>-0,13; 10,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,9</t>
+          <t>-5,45; 4,59</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 45,57</t>
+          <t>-13,63; 47,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 36,23</t>
+          <t>-21,49; 34,02</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 14,6</t>
+          <t>-38,55; 17,02</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 94,27</t>
+          <t>-6,19; 95,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,84; 111,27</t>
+          <t>8,55; 103,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 57,72</t>
+          <t>-21,78; 59,24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,85; 51,52</t>
+          <t>0,85; 52,3</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>1,12; 50,55</t>
+          <t>-0,47; 51,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 24,0</t>
+          <t>-22,4; 22,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6906-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,77</t>
+          <t>-16,49</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-7,46</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 32,81</t>
+          <t>-9,7; 33,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 20,92</t>
+          <t>-21,35; 18,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 17,06</t>
+          <t>-34,77; 7,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 39,14</t>
+          <t>-13,61; 35,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 41,79</t>
+          <t>-5,34; 43,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 36,05</t>
+          <t>-18,46; 31,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 29,03</t>
+          <t>-7,53; 28,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 22,91</t>
+          <t>-8,4; 22,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 17,07</t>
+          <t>-24,42; 8,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,18%</t>
+          <t>-46,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,68%</t>
+          <t>-22,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 141,44</t>
+          <t>-23,85; 139,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 90,33</t>
+          <t>-43,05; 74,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 75,77</t>
+          <t>-80,98; 43,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 319,8</t>
+          <t>-35,15; 227,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 297,08</t>
+          <t>-15,09; 361,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 286,54</t>
+          <t>-48,85; 242,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 121,43</t>
+          <t>-17,42; 115,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 93,77</t>
+          <t>-20,0; 91,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 78,39</t>
+          <t>-59,56; 38,09</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,29</t>
+          <t>16,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 25,02</t>
+          <t>-10,09; 23,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 7,44</t>
+          <t>-22,99; 5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 26,57</t>
+          <t>-8,93; 30,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 23,69</t>
+          <t>-16,99; 21,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 25,99</t>
+          <t>-12,89; 24,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 33,97</t>
+          <t>-2,71; 34,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 18,07</t>
+          <t>-8,46; 19,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 9,64</t>
+          <t>-13,42; 9,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 23,84</t>
+          <t>-2,95; 25,85</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 168,07</t>
+          <t>-32,49; 153,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 61,96</t>
+          <t>-68,46; 46,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 184,95</t>
+          <t>-35,31; 173,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,99; 288,18</t>
+          <t>-63,76; 234,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 350,91</t>
+          <t>-46,91; 292,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 439,67</t>
+          <t>-17,12; 381,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 114,64</t>
+          <t>-31,16; 119,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 66,48</t>
+          <t>-47,6; 62,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 150,23</t>
+          <t>-12,08; 171,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>9,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 31,41</t>
+          <t>-11,91; 32,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 0,0</t>
+          <t>-30,04; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 11,73</t>
+          <t>-21,09; 12,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 40,19</t>
+          <t>-11,81; 40,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 34,94</t>
+          <t>-18,89; 41,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 25,27</t>
+          <t>-11,17; 24,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 26,43</t>
+          <t>-7,51; 25,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 8,41</t>
+          <t>-23,65; 7,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 14,41</t>
+          <t>-8,98; 14,02</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,24%</t>
+          <t>-14,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 458,9</t>
+          <t>-53,52; 455,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 176,2</t>
+          <t>-75,53; 255,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 891,1</t>
+          <t>-61,64; 1103,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 615,82</t>
+          <t>-42,02; 564,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 286,93</t>
+          <t>-33,68; 297,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,79</t>
+          <t>-100,0; 132,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 152,73</t>
+          <t>-38,16; 173,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>13,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,27</t>
+          <t>25,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>17,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 28,38</t>
+          <t>-6,85; 30,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 47,24</t>
+          <t>5,55; 47,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 33,92</t>
+          <t>-6,58; 37,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 46,16</t>
+          <t>2,05; 46,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 52,97</t>
+          <t>12,32; 55,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 31,31</t>
+          <t>5,22; 40,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 29,12</t>
+          <t>1,33; 30,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 43,9</t>
+          <t>12,02; 42,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 21,18</t>
+          <t>3,61; 32,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>120,96%</t>
+          <t>276,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>103,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 246,72</t>
+          <t>-26,63; 241,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,38; 375,62</t>
+          <t>14,33; 360,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 272,2</t>
+          <t>-28,82; 275,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,21; —</t>
+          <t>-16,21; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,17; —</t>
+          <t>15,93; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,07; —</t>
+          <t>5,92; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 251,08</t>
+          <t>0,83; 286,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,56; 417,06</t>
+          <t>47,51; 393,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 166,32</t>
+          <t>10,19; 302,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 12,39</t>
+          <t>-21,39; 12,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 53,56</t>
+          <t>-4,05; 56,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 14,73</t>
+          <t>-20,94; 13,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 44,32</t>
+          <t>-34,65; 42,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 68,73</t>
+          <t>-24,04; 69,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 12,02</t>
+          <t>-52,03; 12,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 19,11</t>
+          <t>-12,83; 21,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 48,45</t>
+          <t>-2,64; 47,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 10,66</t>
+          <t>-18,6; 9,51</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-9,49%</t>
+          <t>-18,05%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,91%</t>
+          <t>-35,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,53%</t>
+          <t>-22,96%</t>
         </is>
       </c>
     </row>
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-84,56; 417,82</t>
+          <t>-78,88; 536,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 1160,82</t>
+          <t>-41,66; 914,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 364,17</t>
+          <t>-82,03; 291,69</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,25</t>
+          <t>10,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 11,52</t>
+          <t>-23,48; 11,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 4,18</t>
+          <t>-29,56; 5,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 11,62</t>
+          <t>-24,0; 10,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 47,35</t>
+          <t>-9,72; 47,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 80,43</t>
+          <t>6,01; 81,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 31,6</t>
+          <t>-15,72; 31,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 16,24</t>
+          <t>-14,42; 14,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 22,17</t>
+          <t>-16,48; 20,96</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 14,95</t>
+          <t>-13,93; 13,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-23,96%</t>
+          <t>-29,21%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-76,04; 108,61</t>
+          <t>-71,48; 110,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,81</t>
+          <t>-100,0; 80,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,49; 123,23</t>
+          <t>-77,2; 100,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-72,25; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,88; —</t>
+          <t>-9,21; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,93; —</t>
+          <t>-49,05; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 137,63</t>
+          <t>-51,67; 143,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-69,82; 182,35</t>
+          <t>-65,72; 169,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 126,29</t>
+          <t>-49,29; 130,33</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>7,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 22,02</t>
+          <t>-7,51; 23,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 15,03</t>
+          <t>-12,73; 14,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 14,91</t>
+          <t>-7,59; 19,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 19,41</t>
+          <t>-18,25; 21,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 18,2</t>
+          <t>-19,09; 17,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 23,0</t>
+          <t>-9,1; 24,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 16,97</t>
+          <t>-5,82; 17,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 12,41</t>
+          <t>-8,52; 11,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 15,08</t>
+          <t>-2,67; 17,64</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 178,27</t>
+          <t>-34,53; 216,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 137,05</t>
+          <t>-55,79; 120,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 128,37</t>
+          <t>-36,11; 160,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 118,85</t>
+          <t>-50,38; 133,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 111,98</t>
+          <t>-52,54; 111,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 142,32</t>
+          <t>-24,39; 160,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 105,29</t>
+          <t>-23,79; 106,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 83,53</t>
+          <t>-35,23; 74,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 94,9</t>
+          <t>-10,99; 114,43</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-18,09</t>
+          <t>-18,42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-14,66</t>
+          <t>-13,74</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-16,15</t>
+          <t>-16,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 4,68</t>
+          <t>-23,79; 3,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 21,94</t>
+          <t>-15,28; 19,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -6,95</t>
+          <t>-29,46; -6,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 25,17</t>
+          <t>-20,75; 23,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 18,33</t>
+          <t>-26,03; 17,58</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-30,32; -0,18</t>
+          <t>-29,34; 0,96</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 5,21</t>
+          <t>-19,21; 4,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 13,83</t>
+          <t>-14,61; 13,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -7,25</t>
+          <t>-24,64; -7,2</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-66,72%</t>
+          <t>-67,95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-51,38%</t>
+          <t>-48,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-58,62%</t>
+          <t>-58,21%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-82,55; 22,18</t>
+          <t>-76,83; 23,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 96,79</t>
+          <t>-47,51; 90,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,1; -20,5</t>
+          <t>-89,05; -23,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,78; 127,29</t>
+          <t>-62,73; 121,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 87,11</t>
+          <t>-78,68; 96,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 0,69</t>
+          <t>-78,44; 8,39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 23,06</t>
+          <t>-61,49; 25,03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 65,52</t>
+          <t>-48,8; 56,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,89; -27,32</t>
+          <t>-77,02; -29,47</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 9,42</t>
+          <t>-2,47; 9,86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,93</t>
+          <t>-5,1; 7,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,13</t>
+          <t>-8,54; 3,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,53</t>
+          <t>-0,37; 15,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,71</t>
+          <t>3,18; 19,01</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,44</t>
+          <t>-1,44; 12,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,42</t>
+          <t>0,02; 9,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 10,11</t>
+          <t>0,24; 10,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,59</t>
+          <t>-2,86; 6,25</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-15,97%</t>
+          <t>-10,96%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 47,86</t>
+          <t>-10,88; 48,34</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 34,02</t>
+          <t>-19,97; 37,24</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 17,02</t>
+          <t>-34,33; 18,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 95,64</t>
+          <t>-2,94; 89,47</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,55; 103,49</t>
+          <t>11,75; 106,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 59,24</t>
+          <t>-5,81; 73,3</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,85; 52,3</t>
+          <t>0,11; 50,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 51,44</t>
+          <t>1,01; 49,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 22,81</t>
+          <t>-11,95; 30,36</t>
         </is>
       </c>
     </row>
